--- a/models/builds/2026-08-07-Patague-tech-services-model.xlsx
+++ b/models/builds/2026-08-07-Patague-tech-services-model.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="131">
   <si>
     <t xml:space="preserve">U.S. Tech Services Firm — FX Transaction Hedge Model</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t xml:space="preserve">12-mo Euribor (EMMI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set to Stage-4 S0_in; nearest listed CME strike</t>
   </si>
   <si>
     <t xml:space="preserve">USD per 1 EUR</t>
@@ -669,28 +672,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -698,135 +705,135 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -975,23 +982,27 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -1123,23 +1134,27 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -1271,23 +1286,27 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -1419,23 +1438,27 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -1545,11 +1568,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="73902982"/>
-        <c:axId val="6897546"/>
+        <c:axId val="77518389"/>
+        <c:axId val="19366816"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="73902982"/>
+        <c:axId val="77518389"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1588,7 +1611,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0000" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1615,7 +1638,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6897546"/>
+        <c:crossAx val="19366816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1623,7 +1646,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6897546"/>
+        <c:axId val="19366816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1672,7 +1695,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="\$#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="\$#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1699,7 +1722,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73902982"/>
+        <c:crossAx val="77518389"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1981,9 +2004,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>448200</xdr:colOff>
+      <xdr:colOff>447840</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>170640</xdr:rowOff>
+      <xdr:rowOff>170280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1991,8 +2014,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="211320" y="4601880"/>
-        <a:ext cx="7919640" cy="3599640"/>
+        <a:off x="211320" y="4600440"/>
+        <a:ext cx="7919280" cy="3599280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2188,147 +2211,147 @@
   <dimension ref="B2:D22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="22"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="s">
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="10" t="n">
         <f aca="false">S0_in*FC_AMT</f>
         <v>13375000</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="8" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="10" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="10" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="8" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="10" t="n">
         <f aca="false">USD_BASE_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="C22" s="12" t="n">
         <f aca="false">USD_FLOOR_PUT</f>
         <v>13153881.9444444</v>
       </c>
@@ -2355,135 +2378,135 @@
   <dimension ref="B2:C20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="5" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="12" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="14" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="15" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="16" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="16" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="16" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="16" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="16" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="16" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="16" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="16" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="16" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="16" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2506,176 +2529,174 @@
   <dimension ref="B2:E15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="44"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="17" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="18" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="18" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="20" t="n">
         <v>12500000</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="18" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="21" t="n">
         <v>1.07</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="18" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="21" t="n">
         <v>1.091</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="18" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="22" t="n">
         <v>0.04</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="18" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="22" t="n">
         <v>0.02</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="18" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="21" t="n">
         <v>1.07</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="10" t="e">
-        <f aca="false">stage-4 S0_in, nearest listed cme strike</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="18" t="s">
+      <c r="E11" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="21" t="n">
         <v>1.07</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="10" t="e">
-        <f aca="false">stage-4 S0_in, nearest listed cme strike</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="18" t="s">
+      <c r="E12" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>0.017</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="10" t="s">
+      <c r="D13" s="9" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="18" t="s">
+      <c r="E13" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="23" t="n">
         <v>0.022</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="10" t="s">
+      <c r="D14" s="9" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="18" t="s">
+      <c r="E14" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="24" t="n">
         <v>365</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="D15" s="9" t="s">
         <v>75</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2697,33 +2718,33 @@
   <dimension ref="B2:C7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="17" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="24" t="n">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="25" t="n">
         <f aca="false">FC_AMT*F0_in</f>
         <v>13637500</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
-        <v>79</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2745,107 +2766,107 @@
   <dimension ref="B2:D16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="5" t="s">
+    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="25" t="n">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="26" t="n">
         <f aca="false">1+R_USD*T_DAYS/360</f>
         <v>1.04055555555556</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="25" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="26" t="n">
         <f aca="false">1+R_FC*T_DAYS/360</f>
         <v>1.02027777777778</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="26" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="27" t="n">
         <f aca="false">FC_AMT/DF_FC</f>
         <v>12251565.4778111</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="27" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="28" t="n">
         <f aca="false">MM_BORROW*S0_in</f>
         <v>13109175.0612578</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="24" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="25" t="n">
         <f aca="false">MM_USD_NOW*DF_USD</f>
         <v>13640824.9387422</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="28" t="n">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="29" t="n">
         <f aca="false">S0_in*DF_USD/DF_FC</f>
         <v>1.09126599509937</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="28" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="29" t="n">
         <f aca="false">ABS(C13-F0_in)</f>
         <v>0.00026599509937375</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="24" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="25" t="n">
         <f aca="false">USD_MM-USD_FWD</f>
         <v>3324.93874217197</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="30" t="n">
         <f aca="false">(USD_MM-USD_FWD)/USD_FWD</f>
         <v>0.000243808523715635</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="30" t="str">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="31" t="str">
         <f aca="false">IF(ABS(USD_MM-USD_FWD)/USD_FWD&lt;=0.0005,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
@@ -2869,65 +2890,65 @@
   <dimension ref="B2:C13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="17" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="27" t="n">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="28" t="n">
         <f aca="false">PREM_PUT*FC_AMT*DF_USD</f>
         <v>221118.055555556</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="24" t="n">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="25" t="n">
         <f aca="false">MAX(S0_in,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="24" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="25" t="n">
         <f aca="false">MIN(Sensitivity!$G$12:$G$22)</f>
         <v>13153881.9444444</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="27" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="28" t="n">
         <f aca="false">K_PUT*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2" t="s">
-        <v>99</v>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2949,509 +2970,509 @@
   <dimension ref="B2:L22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="31" t="n">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="32" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="7" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="C11" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" s="7" t="s">
+      <c r="F11" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="H11" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="I11" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="J11" s="8" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="32" t="n">
+      <c r="K11" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="33" t="n">
         <v>-5</v>
       </c>
-      <c r="C12" s="33" t="n">
+      <c r="C12" s="34" t="n">
         <f aca="false">S0_in*(1+$B12*STEP_FRAC)</f>
         <v>1.0165</v>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D12" s="35" t="n">
         <f aca="false">$C12*FC_AMT</f>
         <v>12706250</v>
       </c>
-      <c r="E12" s="34" t="n">
+      <c r="E12" s="35" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F12" s="35" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G12" s="34" t="n">
+      <c r="G12" s="35" t="n">
         <f aca="false">MAX($C12,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="H12" s="35" t="n">
+      <c r="H12" s="36" t="n">
         <f aca="false">$E12-$D12</f>
         <v>931250</v>
       </c>
-      <c r="I12" s="35" t="n">
+      <c r="I12" s="36" t="n">
         <f aca="false">$F12-$D12</f>
         <v>934574.938742172</v>
       </c>
-      <c r="J12" s="35" t="n">
+      <c r="J12" s="36" t="n">
         <f aca="false">$G12-$D12</f>
         <v>447631.944444444</v>
       </c>
-      <c r="K12" s="14" t="str">
+      <c r="K12" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D12:$G12),$D12:$G12,0))</f>
         <v>Money mkt</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="32" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="33" t="n">
         <v>-4</v>
       </c>
-      <c r="C13" s="33" t="n">
+      <c r="C13" s="34" t="n">
         <f aca="false">S0_in*(1+$B13*STEP_FRAC)</f>
         <v>1.0272</v>
       </c>
-      <c r="D13" s="34" t="n">
+      <c r="D13" s="35" t="n">
         <f aca="false">$C13*FC_AMT</f>
         <v>12840000</v>
       </c>
-      <c r="E13" s="34" t="n">
+      <c r="E13" s="35" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F13" s="34" t="n">
+      <c r="F13" s="35" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G13" s="34" t="n">
+      <c r="G13" s="35" t="n">
         <f aca="false">MAX($C13,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="H13" s="35" t="n">
+      <c r="H13" s="36" t="n">
         <f aca="false">$E13-$D13</f>
         <v>797499.999999998</v>
       </c>
-      <c r="I13" s="35" t="n">
+      <c r="I13" s="36" t="n">
         <f aca="false">$F13-$D13</f>
         <v>800824.93874217</v>
       </c>
-      <c r="J13" s="35" t="n">
+      <c r="J13" s="36" t="n">
         <f aca="false">$G13-$D13</f>
         <v>313881.944444442</v>
       </c>
-      <c r="K13" s="14" t="str">
+      <c r="K13" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D13:$G13),$D13:$G13,0))</f>
         <v>Money mkt</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="32" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="33" t="n">
         <v>-3</v>
       </c>
-      <c r="C14" s="33" t="n">
+      <c r="C14" s="34" t="n">
         <f aca="false">S0_in*(1+$B14*STEP_FRAC)</f>
         <v>1.0379</v>
       </c>
-      <c r="D14" s="34" t="n">
+      <c r="D14" s="35" t="n">
         <f aca="false">$C14*FC_AMT</f>
         <v>12973750</v>
       </c>
-      <c r="E14" s="34" t="n">
+      <c r="E14" s="35" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F14" s="34" t="n">
+      <c r="F14" s="35" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G14" s="34" t="n">
+      <c r="G14" s="35" t="n">
         <f aca="false">MAX($C14,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="H14" s="35" t="n">
+      <c r="H14" s="36" t="n">
         <f aca="false">$E14-$D14</f>
         <v>663750</v>
       </c>
-      <c r="I14" s="35" t="n">
+      <c r="I14" s="36" t="n">
         <f aca="false">$F14-$D14</f>
         <v>667074.938742172</v>
       </c>
-      <c r="J14" s="35" t="n">
+      <c r="J14" s="36" t="n">
         <f aca="false">$G14-$D14</f>
         <v>180131.944444444</v>
       </c>
-      <c r="K14" s="14" t="str">
+      <c r="K14" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D14:$G14),$D14:$G14,0))</f>
         <v>Money mkt</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="32" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="33" t="n">
         <v>-2</v>
       </c>
-      <c r="C15" s="33" t="n">
+      <c r="C15" s="34" t="n">
         <f aca="false">S0_in*(1+$B15*STEP_FRAC)</f>
         <v>1.0486</v>
       </c>
-      <c r="D15" s="34" t="n">
+      <c r="D15" s="35" t="n">
         <f aca="false">$C15*FC_AMT</f>
         <v>13107500</v>
       </c>
-      <c r="E15" s="34" t="n">
+      <c r="E15" s="35" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F15" s="34" t="n">
+      <c r="F15" s="35" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G15" s="34" t="n">
+      <c r="G15" s="35" t="n">
         <f aca="false">MAX($C15,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="H15" s="35" t="n">
+      <c r="H15" s="36" t="n">
         <f aca="false">$E15-$D15</f>
         <v>530000</v>
       </c>
-      <c r="I15" s="35" t="n">
+      <c r="I15" s="36" t="n">
         <f aca="false">$F15-$D15</f>
         <v>533324.938742172</v>
       </c>
-      <c r="J15" s="35" t="n">
+      <c r="J15" s="36" t="n">
         <f aca="false">$G15-$D15</f>
         <v>46381.944444444</v>
       </c>
-      <c r="K15" s="14" t="str">
+      <c r="K15" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D15:$G15),$D15:$G15,0))</f>
         <v>Money mkt</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="32" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="33" t="n">
         <v>-1</v>
       </c>
-      <c r="C16" s="33" t="n">
+      <c r="C16" s="34" t="n">
         <f aca="false">S0_in*(1+$B16*STEP_FRAC)</f>
         <v>1.0593</v>
       </c>
-      <c r="D16" s="34" t="n">
+      <c r="D16" s="35" t="n">
         <f aca="false">$C16*FC_AMT</f>
         <v>13241250</v>
       </c>
-      <c r="E16" s="34" t="n">
+      <c r="E16" s="35" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F16" s="34" t="n">
+      <c r="F16" s="35" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G16" s="34" t="n">
+      <c r="G16" s="35" t="n">
         <f aca="false">MAX($C16,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="H16" s="35" t="n">
+      <c r="H16" s="36" t="n">
         <f aca="false">$E16-$D16</f>
         <v>396249.999999998</v>
       </c>
-      <c r="I16" s="35" t="n">
+      <c r="I16" s="36" t="n">
         <f aca="false">$F16-$D16</f>
         <v>399574.93874217</v>
       </c>
-      <c r="J16" s="35" t="n">
+      <c r="J16" s="36" t="n">
         <f aca="false">$G16-$D16</f>
         <v>-87368.0555555578</v>
       </c>
-      <c r="K16" s="14" t="str">
+      <c r="K16" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D16:$G16),$D16:$G16,0))</f>
         <v>Money mkt</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="32" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="33" t="n">
+      <c r="C17" s="34" t="n">
         <f aca="false">S0_in*(1+$B17*STEP_FRAC)</f>
         <v>1.07</v>
       </c>
-      <c r="D17" s="34" t="n">
+      <c r="D17" s="35" t="n">
         <f aca="false">$C17*FC_AMT</f>
         <v>13375000</v>
       </c>
-      <c r="E17" s="34" t="n">
+      <c r="E17" s="35" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F17" s="34" t="n">
+      <c r="F17" s="35" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G17" s="34" t="n">
+      <c r="G17" s="35" t="n">
         <f aca="false">MAX($C17,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="H17" s="35" t="n">
+      <c r="H17" s="36" t="n">
         <f aca="false">$E17-$D17</f>
         <v>262500</v>
       </c>
-      <c r="I17" s="35" t="n">
+      <c r="I17" s="36" t="n">
         <f aca="false">$F17-$D17</f>
         <v>265824.938742172</v>
       </c>
-      <c r="J17" s="35" t="n">
+      <c r="J17" s="36" t="n">
         <f aca="false">$G17-$D17</f>
         <v>-221118.055555556</v>
       </c>
-      <c r="K17" s="14" t="str">
+      <c r="K17" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D17:$G17),$D17:$G17,0))</f>
         <v>Money mkt</v>
       </c>
-      <c r="L17" s="36" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="32" t="n">
+      <c r="L17" s="37" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="33" t="n">
+      <c r="C18" s="34" t="n">
         <f aca="false">S0_in*(1+$B18*STEP_FRAC)</f>
         <v>1.0807</v>
       </c>
-      <c r="D18" s="34" t="n">
+      <c r="D18" s="35" t="n">
         <f aca="false">$C18*FC_AMT</f>
         <v>13508750</v>
       </c>
-      <c r="E18" s="34" t="n">
+      <c r="E18" s="35" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F18" s="34" t="n">
+      <c r="F18" s="35" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G18" s="34" t="n">
+      <c r="G18" s="35" t="n">
         <f aca="false">MAX($C18,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13287631.9444444</v>
       </c>
-      <c r="H18" s="35" t="n">
+      <c r="H18" s="36" t="n">
         <f aca="false">$E18-$D18</f>
         <v>128750</v>
       </c>
-      <c r="I18" s="35" t="n">
+      <c r="I18" s="36" t="n">
         <f aca="false">$F18-$D18</f>
         <v>132074.938742172</v>
       </c>
-      <c r="J18" s="35" t="n">
+      <c r="J18" s="36" t="n">
         <f aca="false">$G18-$D18</f>
         <v>-221118.055555556</v>
       </c>
-      <c r="K18" s="14" t="str">
+      <c r="K18" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D18:$G18),$D18:$G18,0))</f>
         <v>Money mkt</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="32" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="33" t="n">
+      <c r="C19" s="34" t="n">
         <f aca="false">S0_in*(1+$B19*STEP_FRAC)</f>
         <v>1.0914</v>
       </c>
-      <c r="D19" s="34" t="n">
+      <c r="D19" s="35" t="n">
         <f aca="false">$C19*FC_AMT</f>
         <v>13642500</v>
       </c>
-      <c r="E19" s="34" t="n">
+      <c r="E19" s="35" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F19" s="34" t="n">
+      <c r="F19" s="35" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G19" s="34" t="n">
+      <c r="G19" s="35" t="n">
         <f aca="false">MAX($C19,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13421381.9444444</v>
       </c>
-      <c r="H19" s="35" t="n">
+      <c r="H19" s="36" t="n">
         <f aca="false">$E19-$D19</f>
         <v>-5000.00000000186</v>
       </c>
-      <c r="I19" s="35" t="n">
+      <c r="I19" s="36" t="n">
         <f aca="false">$F19-$D19</f>
         <v>-1675.06125782989</v>
       </c>
-      <c r="J19" s="35" t="n">
+      <c r="J19" s="36" t="n">
         <f aca="false">$G19-$D19</f>
         <v>-221118.055555556</v>
       </c>
-      <c r="K19" s="14" t="str">
+      <c r="K19" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D19:$G19),$D19:$G19,0))</f>
         <v>No hedge</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="32" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="33" t="n">
+      <c r="C20" s="34" t="n">
         <f aca="false">S0_in*(1+$B20*STEP_FRAC)</f>
         <v>1.1021</v>
       </c>
-      <c r="D20" s="34" t="n">
+      <c r="D20" s="35" t="n">
         <f aca="false">$C20*FC_AMT</f>
         <v>13776250</v>
       </c>
-      <c r="E20" s="34" t="n">
+      <c r="E20" s="35" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F20" s="34" t="n">
+      <c r="F20" s="35" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G20" s="34" t="n">
+      <c r="G20" s="35" t="n">
         <f aca="false">MAX($C20,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13555131.9444444</v>
       </c>
-      <c r="H20" s="35" t="n">
+      <c r="H20" s="36" t="n">
         <f aca="false">$E20-$D20</f>
         <v>-138750.000000002</v>
       </c>
-      <c r="I20" s="35" t="n">
+      <c r="I20" s="36" t="n">
         <f aca="false">$F20-$D20</f>
         <v>-135425.06125783</v>
       </c>
-      <c r="J20" s="35" t="n">
+      <c r="J20" s="36" t="n">
         <f aca="false">$G20-$D20</f>
         <v>-221118.055555556</v>
       </c>
-      <c r="K20" s="14" t="str">
+      <c r="K20" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D20:$G20),$D20:$G20,0))</f>
         <v>No hedge</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="32" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="33" t="n">
+      <c r="C21" s="34" t="n">
         <f aca="false">S0_in*(1+$B21*STEP_FRAC)</f>
         <v>1.1128</v>
       </c>
-      <c r="D21" s="34" t="n">
+      <c r="D21" s="35" t="n">
         <f aca="false">$C21*FC_AMT</f>
         <v>13910000</v>
       </c>
-      <c r="E21" s="34" t="n">
+      <c r="E21" s="35" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F21" s="34" t="n">
+      <c r="F21" s="35" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G21" s="34" t="n">
+      <c r="G21" s="35" t="n">
         <f aca="false">MAX($C21,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13688881.9444444</v>
       </c>
-      <c r="H21" s="35" t="n">
+      <c r="H21" s="36" t="n">
         <f aca="false">$E21-$D21</f>
         <v>-272500</v>
       </c>
-      <c r="I21" s="35" t="n">
+      <c r="I21" s="36" t="n">
         <f aca="false">$F21-$D21</f>
         <v>-269175.061257828</v>
       </c>
-      <c r="J21" s="35" t="n">
+      <c r="J21" s="36" t="n">
         <f aca="false">$G21-$D21</f>
         <v>-221118.055555556</v>
       </c>
-      <c r="K21" s="14" t="str">
+      <c r="K21" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D21:$G21),$D21:$G21,0))</f>
         <v>No hedge</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="32" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="33" t="n">
+      <c r="C22" s="34" t="n">
         <f aca="false">S0_in*(1+$B22*STEP_FRAC)</f>
         <v>1.1235</v>
       </c>
-      <c r="D22" s="34" t="n">
+      <c r="D22" s="35" t="n">
         <f aca="false">$C22*FC_AMT</f>
         <v>14043750</v>
       </c>
-      <c r="E22" s="34" t="n">
+      <c r="E22" s="35" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F22" s="34" t="n">
+      <c r="F22" s="35" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G22" s="34" t="n">
+      <c r="G22" s="35" t="n">
         <f aca="false">MAX($C22,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13822631.9444444</v>
       </c>
-      <c r="H22" s="35" t="n">
+      <c r="H22" s="36" t="n">
         <f aca="false">$E22-$D22</f>
         <v>-406250.000000002</v>
       </c>
-      <c r="I22" s="35" t="n">
+      <c r="I22" s="36" t="n">
         <f aca="false">$F22-$D22</f>
         <v>-402925.06125783</v>
       </c>
-      <c r="J22" s="35" t="n">
+      <c r="J22" s="36" t="n">
         <f aca="false">$G22-$D22</f>
         <v>-221118.055555556</v>
       </c>
-      <c r="K22" s="14" t="str">
+      <c r="K22" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D22:$G22),$D22:$G22,0))</f>
         <v>No hedge</v>
       </c>
@@ -3476,178 +3497,178 @@
   <dimension ref="B2:E19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="7" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="s">
+      <c r="E12" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="37" t="n">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="38" t="n">
         <f aca="false">S0_in*DF_USD/DF_FC</f>
         <v>1.09126599509937</v>
       </c>
-      <c r="D13" s="37" t="n">
+      <c r="D13" s="38" t="n">
         <f aca="false">F0_in</f>
         <v>1.091</v>
       </c>
-      <c r="E13" s="14" t="str">
+      <c r="E13" s="15" t="str">
         <f aca="false">IF(ABS(C13-D13)&lt;=0.0025,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" s="38" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="39" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="D14" s="38" t="n">
+      <c r="D14" s="39" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="E14" s="14" t="str">
+      <c r="E14" s="15" t="str">
         <f aca="false">IF(ABS(C14-D14)/D14&lt;=0.0005,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C15" s="38" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="39" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="D15" s="39" t="n">
+      <c r="D15" s="40" t="n">
         <v>13637500</v>
       </c>
-      <c r="E15" s="14" t="str">
+      <c r="E15" s="15" t="str">
         <f aca="false">IF(ABS(C15-D15)&lt;=1,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16" s="38" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="39" t="n">
         <f aca="false">FV_PREM_PUT</f>
         <v>221118.055555556</v>
       </c>
-      <c r="D16" s="39" t="n">
+      <c r="D16" s="40" t="n">
         <v>221118.06</v>
       </c>
-      <c r="E16" s="14" t="str">
+      <c r="E16" s="15" t="str">
         <f aca="false">IF(ABS(C16-D16)&lt;=1,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C17" s="38" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="39" t="n">
         <f aca="false">MAX(K_PUT,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="D17" s="38" t="n">
+      <c r="D17" s="39" t="n">
         <f aca="false">K_PUT*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="E17" s="14" t="str">
+      <c r="E17" s="15" t="str">
         <f aca="false">IF(ABS(C17-D17)&lt;=0.01,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C18" s="38" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="39" t="n">
         <f aca="false">S0_in*FC_AMT</f>
         <v>13375000</v>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D18" s="40" t="n">
         <v>13375000</v>
       </c>
-      <c r="E18" s="14" t="str">
+      <c r="E18" s="15" t="str">
         <f aca="false">IF(ABS(C18-D18)&lt;=1,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="C19" s="33" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="34" t="n">
         <f aca="false">Sensitivity!$C$12+Sensitivity!$C$22</f>
         <v>2.14</v>
       </c>
-      <c r="D19" s="33" t="n">
+      <c r="D19" s="34" t="n">
         <f aca="false">2*S0_in</f>
         <v>2.14</v>
       </c>
-      <c r="E19" s="14" t="str">
+      <c r="E19" s="15" t="str">
         <f aca="false">IF(ABS(C19-D19)&lt;=0.000001,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>

--- a/models/builds/2026-08-07-Patague-tech-services-model.xlsx
+++ b/models/builds/2026-08-07-Patague-tech-services-model.xlsx
@@ -22,6 +22,7 @@
     <definedName function="false" hidden="false" name="DF_USD" vbProcedure="false">MM_Hedge!$C$5</definedName>
     <definedName function="false" hidden="false" name="F0_in" vbProcedure="false">Inputs!$C$8</definedName>
     <definedName function="false" hidden="false" name="FC_AMT" vbProcedure="false">Inputs!$C$6</definedName>
+    <definedName function="false" hidden="false" name="FV_PREM_CALL" vbProcedure="false">Opt_Hedge!$C$16</definedName>
     <definedName function="false" hidden="false" name="FV_PREM_PUT" vbProcedure="false">Opt_Hedge!$C$5</definedName>
     <definedName function="false" hidden="false" name="K_CALL" vbProcedure="false">Inputs!$C$12</definedName>
     <definedName function="false" hidden="false" name="K_PUT" vbProcedure="false">Inputs!$C$11</definedName>
@@ -37,6 +38,7 @@
     <definedName function="false" hidden="false" name="STEP_FRAC" vbProcedure="false">Sensitivity!$C$4</definedName>
     <definedName function="false" hidden="false" name="S_T_grid" vbProcedure="false">Sensitivity!$C$12:$C$22</definedName>
     <definedName function="false" hidden="false" name="T_DAYS" vbProcedure="false">Inputs!$C$15</definedName>
+    <definedName function="false" hidden="false" name="USD_BASE_CALL" vbProcedure="false">Opt_Hedge!$C$17</definedName>
     <definedName function="false" hidden="false" name="USD_BASE_PUT" vbProcedure="false">Opt_Hedge!$C$9</definedName>
     <definedName function="false" hidden="false" name="USD_FLOOR_PUT" vbProcedure="false">Opt_Hedge!$C$10</definedName>
     <definedName function="false" hidden="false" name="USD_FWD" vbProcedure="false">Fwd_Hedge!$C$5</definedName>
@@ -52,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="136">
   <si>
     <t xml:space="preserve">U.S. Tech Services Firm — FX Transaction Hedge Model</t>
   </si>
@@ -357,6 +359,24 @@
     <t xml:space="preserve">Full payoff across the grid: Sensitivity tab, column G.</t>
   </si>
   <si>
+    <t xml:space="preserve">Call hedge — payable-side variant (§5.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FV_PREM_CALL = PREM_CALL × FC_AMT × DF_USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline outlay (S_T = S0_in): USD_CALL = MIN(S_T,K_CALL)×FC_AMT + FV_PREM_CALL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD_CALL as a function of S_T (grid mirrors Sensitivity)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S_T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD_CALL outlay</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sensitivity — S_T grid ±5% in 1% steps (§6)</t>
   </si>
   <si>
@@ -364,9 +384,6 @@
   </si>
   <si>
     <t xml:space="preserve">n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S_T</t>
   </si>
   <si>
     <t xml:space="preserve">Money mkt</t>
@@ -451,7 +468,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="15">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
@@ -463,8 +480,10 @@
     <numFmt numFmtId="172" formatCode="0.000000"/>
     <numFmt numFmtId="173" formatCode="0.00000"/>
     <numFmt numFmtId="174" formatCode="0.0000%"/>
-    <numFmt numFmtId="175" formatCode="0.0%"/>
-    <numFmt numFmtId="176" formatCode="\$#,##0;&quot;($&quot;#,##0\)"/>
+    <numFmt numFmtId="175" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="\$#,##0"/>
+    <numFmt numFmtId="177" formatCode="0.0%"/>
+    <numFmt numFmtId="178" formatCode="\$#,##0;&quot;($&quot;#,##0\)"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -672,7 +691,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="48">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -801,7 +820,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -817,7 +864,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1568,11 +1615,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="77518389"/>
-        <c:axId val="19366816"/>
+        <c:axId val="47287402"/>
+        <c:axId val="63147692"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="77518389"/>
+        <c:axId val="47287402"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1638,7 +1685,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19366816"/>
+        <c:crossAx val="63147692"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1646,7 +1693,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19366816"/>
+        <c:axId val="63147692"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1722,7 +1769,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77518389"/>
+        <c:crossAx val="47287402"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2004,9 +2051,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>447840</xdr:colOff>
+      <xdr:colOff>447480</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>170280</xdr:rowOff>
+      <xdr:rowOff>169920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2015,7 +2062,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="211320" y="4600440"/>
-        <a:ext cx="7919280" cy="3599280"/>
+        <a:ext cx="7918920" cy="3598920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2887,7 +2934,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C13"/>
+  <dimension ref="B2:C31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
@@ -2949,6 +2996,152 @@
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="34" t="n">
+        <f aca="false">PREM_CALL*FC_AMT*DF_USD</f>
+        <v>286152.777777778</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="35" t="n">
+        <f aca="false">MIN(S0_in,K_CALL)*FC_AMT+FV_PREM_CALL</f>
+        <v>13661152.7777778</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="33" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="37" t="n">
+        <f aca="false">Sensitivity!$C$12</f>
+        <v>1.0165</v>
+      </c>
+      <c r="C21" s="38" t="n">
+        <f aca="false">MIN($B21,K_CALL)*FC_AMT+FV_PREM_CALL</f>
+        <v>12992402.7777778</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="37" t="n">
+        <f aca="false">Sensitivity!$C$13</f>
+        <v>1.0272</v>
+      </c>
+      <c r="C22" s="38" t="n">
+        <f aca="false">MIN($B22,K_CALL)*FC_AMT+FV_PREM_CALL</f>
+        <v>13126152.7777778</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="37" t="n">
+        <f aca="false">Sensitivity!$C$14</f>
+        <v>1.0379</v>
+      </c>
+      <c r="C23" s="38" t="n">
+        <f aca="false">MIN($B23,K_CALL)*FC_AMT+FV_PREM_CALL</f>
+        <v>13259902.7777778</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="37" t="n">
+        <f aca="false">Sensitivity!$C$15</f>
+        <v>1.0486</v>
+      </c>
+      <c r="C24" s="38" t="n">
+        <f aca="false">MIN($B24,K_CALL)*FC_AMT+FV_PREM_CALL</f>
+        <v>13393652.7777778</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="37" t="n">
+        <f aca="false">Sensitivity!$C$16</f>
+        <v>1.0593</v>
+      </c>
+      <c r="C25" s="38" t="n">
+        <f aca="false">MIN($B25,K_CALL)*FC_AMT+FV_PREM_CALL</f>
+        <v>13527402.7777778</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="37" t="n">
+        <f aca="false">Sensitivity!$C$17</f>
+        <v>1.07</v>
+      </c>
+      <c r="C26" s="38" t="n">
+        <f aca="false">MIN($B26,K_CALL)*FC_AMT+FV_PREM_CALL</f>
+        <v>13661152.7777778</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="37" t="n">
+        <f aca="false">Sensitivity!$C$18</f>
+        <v>1.0807</v>
+      </c>
+      <c r="C27" s="38" t="n">
+        <f aca="false">MIN($B27,K_CALL)*FC_AMT+FV_PREM_CALL</f>
+        <v>13661152.7777778</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="37" t="n">
+        <f aca="false">Sensitivity!$C$19</f>
+        <v>1.0914</v>
+      </c>
+      <c r="C28" s="38" t="n">
+        <f aca="false">MIN($B28,K_CALL)*FC_AMT+FV_PREM_CALL</f>
+        <v>13661152.7777778</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="37" t="n">
+        <f aca="false">Sensitivity!$C$20</f>
+        <v>1.1021</v>
+      </c>
+      <c r="C29" s="38" t="n">
+        <f aca="false">MIN($B29,K_CALL)*FC_AMT+FV_PREM_CALL</f>
+        <v>13661152.7777778</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="37" t="n">
+        <f aca="false">Sensitivity!$C$21</f>
+        <v>1.1128</v>
+      </c>
+      <c r="C30" s="38" t="n">
+        <f aca="false">MIN($B30,K_CALL)*FC_AMT+FV_PREM_CALL</f>
+        <v>13661152.7777778</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="37" t="n">
+        <f aca="false">Sensitivity!$C$22</f>
+        <v>1.1235</v>
+      </c>
+      <c r="C31" s="38" t="n">
+        <f aca="false">MIN($B31,K_CALL)*FC_AMT+FV_PREM_CALL</f>
+        <v>13661152.7777778</v>
       </c>
     </row>
   </sheetData>
@@ -2980,23 +3173,23 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="32" t="n">
+        <v>108</v>
+      </c>
+      <c r="C4" s="39" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>18</v>
@@ -3005,57 +3198,57 @@
         <v>20</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="33" t="n">
+      <c r="B12" s="40" t="n">
         <v>-5</v>
       </c>
-      <c r="C12" s="34" t="n">
+      <c r="C12" s="41" t="n">
         <f aca="false">S0_in*(1+$B12*STEP_FRAC)</f>
         <v>1.0165</v>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="42" t="n">
         <f aca="false">$C12*FC_AMT</f>
         <v>12706250</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="42" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F12" s="35" t="n">
+      <c r="F12" s="42" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G12" s="35" t="n">
+      <c r="G12" s="42" t="n">
         <f aca="false">MAX($C12,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="H12" s="36" t="n">
+      <c r="H12" s="43" t="n">
         <f aca="false">$E12-$D12</f>
         <v>931250</v>
       </c>
-      <c r="I12" s="36" t="n">
+      <c r="I12" s="43" t="n">
         <f aca="false">$F12-$D12</f>
         <v>934574.938742172</v>
       </c>
-      <c r="J12" s="36" t="n">
+      <c r="J12" s="43" t="n">
         <f aca="false">$G12-$D12</f>
         <v>447631.944444444</v>
       </c>
@@ -3065,38 +3258,38 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="33" t="n">
+      <c r="B13" s="40" t="n">
         <v>-4</v>
       </c>
-      <c r="C13" s="34" t="n">
+      <c r="C13" s="41" t="n">
         <f aca="false">S0_in*(1+$B13*STEP_FRAC)</f>
         <v>1.0272</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="42" t="n">
         <f aca="false">$C13*FC_AMT</f>
         <v>12840000</v>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="42" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F13" s="35" t="n">
+      <c r="F13" s="42" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G13" s="35" t="n">
+      <c r="G13" s="42" t="n">
         <f aca="false">MAX($C13,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="H13" s="36" t="n">
+      <c r="H13" s="43" t="n">
         <f aca="false">$E13-$D13</f>
         <v>797499.999999998</v>
       </c>
-      <c r="I13" s="36" t="n">
+      <c r="I13" s="43" t="n">
         <f aca="false">$F13-$D13</f>
         <v>800824.93874217</v>
       </c>
-      <c r="J13" s="36" t="n">
+      <c r="J13" s="43" t="n">
         <f aca="false">$G13-$D13</f>
         <v>313881.944444442</v>
       </c>
@@ -3106,38 +3299,38 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="33" t="n">
+      <c r="B14" s="40" t="n">
         <v>-3</v>
       </c>
-      <c r="C14" s="34" t="n">
+      <c r="C14" s="41" t="n">
         <f aca="false">S0_in*(1+$B14*STEP_FRAC)</f>
         <v>1.0379</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="42" t="n">
         <f aca="false">$C14*FC_AMT</f>
         <v>12973750</v>
       </c>
-      <c r="E14" s="35" t="n">
+      <c r="E14" s="42" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F14" s="35" t="n">
+      <c r="F14" s="42" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G14" s="35" t="n">
+      <c r="G14" s="42" t="n">
         <f aca="false">MAX($C14,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="H14" s="36" t="n">
+      <c r="H14" s="43" t="n">
         <f aca="false">$E14-$D14</f>
         <v>663750</v>
       </c>
-      <c r="I14" s="36" t="n">
+      <c r="I14" s="43" t="n">
         <f aca="false">$F14-$D14</f>
         <v>667074.938742172</v>
       </c>
-      <c r="J14" s="36" t="n">
+      <c r="J14" s="43" t="n">
         <f aca="false">$G14-$D14</f>
         <v>180131.944444444</v>
       </c>
@@ -3147,38 +3340,38 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="33" t="n">
+      <c r="B15" s="40" t="n">
         <v>-2</v>
       </c>
-      <c r="C15" s="34" t="n">
+      <c r="C15" s="41" t="n">
         <f aca="false">S0_in*(1+$B15*STEP_FRAC)</f>
         <v>1.0486</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="42" t="n">
         <f aca="false">$C15*FC_AMT</f>
         <v>13107500</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="42" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="42" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G15" s="35" t="n">
+      <c r="G15" s="42" t="n">
         <f aca="false">MAX($C15,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="H15" s="36" t="n">
+      <c r="H15" s="43" t="n">
         <f aca="false">$E15-$D15</f>
         <v>530000</v>
       </c>
-      <c r="I15" s="36" t="n">
+      <c r="I15" s="43" t="n">
         <f aca="false">$F15-$D15</f>
         <v>533324.938742172</v>
       </c>
-      <c r="J15" s="36" t="n">
+      <c r="J15" s="43" t="n">
         <f aca="false">$G15-$D15</f>
         <v>46381.944444444</v>
       </c>
@@ -3188,38 +3381,38 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="33" t="n">
+      <c r="B16" s="40" t="n">
         <v>-1</v>
       </c>
-      <c r="C16" s="34" t="n">
+      <c r="C16" s="41" t="n">
         <f aca="false">S0_in*(1+$B16*STEP_FRAC)</f>
         <v>1.0593</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="42" t="n">
         <f aca="false">$C16*FC_AMT</f>
         <v>13241250</v>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E16" s="42" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F16" s="35" t="n">
+      <c r="F16" s="42" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G16" s="35" t="n">
+      <c r="G16" s="42" t="n">
         <f aca="false">MAX($C16,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="H16" s="36" t="n">
+      <c r="H16" s="43" t="n">
         <f aca="false">$E16-$D16</f>
         <v>396249.999999998</v>
       </c>
-      <c r="I16" s="36" t="n">
+      <c r="I16" s="43" t="n">
         <f aca="false">$F16-$D16</f>
         <v>399574.93874217</v>
       </c>
-      <c r="J16" s="36" t="n">
+      <c r="J16" s="43" t="n">
         <f aca="false">$G16-$D16</f>
         <v>-87368.0555555578</v>
       </c>
@@ -3229,38 +3422,38 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="33" t="n">
+      <c r="B17" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="34" t="n">
+      <c r="C17" s="41" t="n">
         <f aca="false">S0_in*(1+$B17*STEP_FRAC)</f>
         <v>1.07</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="42" t="n">
         <f aca="false">$C17*FC_AMT</f>
         <v>13375000</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="42" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="42" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G17" s="35" t="n">
+      <c r="G17" s="42" t="n">
         <f aca="false">MAX($C17,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="H17" s="36" t="n">
+      <c r="H17" s="43" t="n">
         <f aca="false">$E17-$D17</f>
         <v>262500</v>
       </c>
-      <c r="I17" s="36" t="n">
+      <c r="I17" s="43" t="n">
         <f aca="false">$F17-$D17</f>
         <v>265824.938742172</v>
       </c>
-      <c r="J17" s="36" t="n">
+      <c r="J17" s="43" t="n">
         <f aca="false">$G17-$D17</f>
         <v>-221118.055555556</v>
       </c>
@@ -3268,43 +3461,43 @@
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D17:$G17),$D17:$G17,0))</f>
         <v>Money mkt</v>
       </c>
-      <c r="L17" s="37" t="s">
-        <v>111</v>
+      <c r="L17" s="44" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="33" t="n">
+      <c r="B18" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="34" t="n">
+      <c r="C18" s="41" t="n">
         <f aca="false">S0_in*(1+$B18*STEP_FRAC)</f>
         <v>1.0807</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="42" t="n">
         <f aca="false">$C18*FC_AMT</f>
         <v>13508750</v>
       </c>
-      <c r="E18" s="35" t="n">
+      <c r="E18" s="42" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F18" s="35" t="n">
+      <c r="F18" s="42" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G18" s="35" t="n">
+      <c r="G18" s="42" t="n">
         <f aca="false">MAX($C18,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13287631.9444444</v>
       </c>
-      <c r="H18" s="36" t="n">
+      <c r="H18" s="43" t="n">
         <f aca="false">$E18-$D18</f>
         <v>128750</v>
       </c>
-      <c r="I18" s="36" t="n">
+      <c r="I18" s="43" t="n">
         <f aca="false">$F18-$D18</f>
         <v>132074.938742172</v>
       </c>
-      <c r="J18" s="36" t="n">
+      <c r="J18" s="43" t="n">
         <f aca="false">$G18-$D18</f>
         <v>-221118.055555556</v>
       </c>
@@ -3314,38 +3507,38 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="33" t="n">
+      <c r="B19" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="34" t="n">
+      <c r="C19" s="41" t="n">
         <f aca="false">S0_in*(1+$B19*STEP_FRAC)</f>
         <v>1.0914</v>
       </c>
-      <c r="D19" s="35" t="n">
+      <c r="D19" s="42" t="n">
         <f aca="false">$C19*FC_AMT</f>
         <v>13642500</v>
       </c>
-      <c r="E19" s="35" t="n">
+      <c r="E19" s="42" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F19" s="35" t="n">
+      <c r="F19" s="42" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G19" s="35" t="n">
+      <c r="G19" s="42" t="n">
         <f aca="false">MAX($C19,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13421381.9444444</v>
       </c>
-      <c r="H19" s="36" t="n">
+      <c r="H19" s="43" t="n">
         <f aca="false">$E19-$D19</f>
         <v>-5000.00000000186</v>
       </c>
-      <c r="I19" s="36" t="n">
+      <c r="I19" s="43" t="n">
         <f aca="false">$F19-$D19</f>
         <v>-1675.06125782989</v>
       </c>
-      <c r="J19" s="36" t="n">
+      <c r="J19" s="43" t="n">
         <f aca="false">$G19-$D19</f>
         <v>-221118.055555556</v>
       </c>
@@ -3355,38 +3548,38 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="33" t="n">
+      <c r="B20" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="34" t="n">
+      <c r="C20" s="41" t="n">
         <f aca="false">S0_in*(1+$B20*STEP_FRAC)</f>
         <v>1.1021</v>
       </c>
-      <c r="D20" s="35" t="n">
+      <c r="D20" s="42" t="n">
         <f aca="false">$C20*FC_AMT</f>
         <v>13776250</v>
       </c>
-      <c r="E20" s="35" t="n">
+      <c r="E20" s="42" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F20" s="35" t="n">
+      <c r="F20" s="42" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G20" s="35" t="n">
+      <c r="G20" s="42" t="n">
         <f aca="false">MAX($C20,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13555131.9444444</v>
       </c>
-      <c r="H20" s="36" t="n">
+      <c r="H20" s="43" t="n">
         <f aca="false">$E20-$D20</f>
         <v>-138750.000000002</v>
       </c>
-      <c r="I20" s="36" t="n">
+      <c r="I20" s="43" t="n">
         <f aca="false">$F20-$D20</f>
         <v>-135425.06125783</v>
       </c>
-      <c r="J20" s="36" t="n">
+      <c r="J20" s="43" t="n">
         <f aca="false">$G20-$D20</f>
         <v>-221118.055555556</v>
       </c>
@@ -3396,38 +3589,38 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="33" t="n">
+      <c r="B21" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="34" t="n">
+      <c r="C21" s="41" t="n">
         <f aca="false">S0_in*(1+$B21*STEP_FRAC)</f>
         <v>1.1128</v>
       </c>
-      <c r="D21" s="35" t="n">
+      <c r="D21" s="42" t="n">
         <f aca="false">$C21*FC_AMT</f>
         <v>13910000</v>
       </c>
-      <c r="E21" s="35" t="n">
+      <c r="E21" s="42" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F21" s="35" t="n">
+      <c r="F21" s="42" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G21" s="35" t="n">
+      <c r="G21" s="42" t="n">
         <f aca="false">MAX($C21,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13688881.9444444</v>
       </c>
-      <c r="H21" s="36" t="n">
+      <c r="H21" s="43" t="n">
         <f aca="false">$E21-$D21</f>
         <v>-272500</v>
       </c>
-      <c r="I21" s="36" t="n">
+      <c r="I21" s="43" t="n">
         <f aca="false">$F21-$D21</f>
         <v>-269175.061257828</v>
       </c>
-      <c r="J21" s="36" t="n">
+      <c r="J21" s="43" t="n">
         <f aca="false">$G21-$D21</f>
         <v>-221118.055555556</v>
       </c>
@@ -3437,38 +3630,38 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="33" t="n">
+      <c r="B22" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="34" t="n">
+      <c r="C22" s="41" t="n">
         <f aca="false">S0_in*(1+$B22*STEP_FRAC)</f>
         <v>1.1235</v>
       </c>
-      <c r="D22" s="35" t="n">
+      <c r="D22" s="42" t="n">
         <f aca="false">$C22*FC_AMT</f>
         <v>14043750</v>
       </c>
-      <c r="E22" s="35" t="n">
+      <c r="E22" s="42" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="F22" s="35" t="n">
+      <c r="F22" s="42" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="G22" s="35" t="n">
+      <c r="G22" s="42" t="n">
         <f aca="false">MAX($C22,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13822631.9444444</v>
       </c>
-      <c r="H22" s="36" t="n">
+      <c r="H22" s="43" t="n">
         <f aca="false">$E22-$D22</f>
         <v>-406250.000000002</v>
       </c>
-      <c r="I22" s="36" t="n">
+      <c r="I22" s="43" t="n">
         <f aca="false">$F22-$D22</f>
         <v>-402925.06125783</v>
       </c>
-      <c r="J22" s="36" t="n">
+      <c r="J22" s="43" t="n">
         <f aca="false">$G22-$D22</f>
         <v>-221118.055555556</v>
       </c>
@@ -3505,67 +3698,67 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="8" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="38" t="n">
+        <v>129</v>
+      </c>
+      <c r="C13" s="45" t="n">
         <f aca="false">S0_in*DF_USD/DF_FC</f>
         <v>1.09126599509937</v>
       </c>
-      <c r="D13" s="38" t="n">
+      <c r="D13" s="45" t="n">
         <f aca="false">F0_in</f>
         <v>1.091</v>
       </c>
@@ -3576,13 +3769,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="39" t="n">
+        <v>130</v>
+      </c>
+      <c r="C14" s="46" t="n">
         <f aca="false">USD_MM</f>
         <v>13640824.9387422</v>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D14" s="46" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
@@ -3593,13 +3786,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" s="39" t="n">
+        <v>131</v>
+      </c>
+      <c r="C15" s="46" t="n">
         <f aca="false">USD_FWD</f>
         <v>13637500</v>
       </c>
-      <c r="D15" s="40" t="n">
+      <c r="D15" s="47" t="n">
         <v>13637500</v>
       </c>
       <c r="E15" s="15" t="str">
@@ -3609,13 +3802,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C16" s="39" t="n">
+        <v>132</v>
+      </c>
+      <c r="C16" s="46" t="n">
         <f aca="false">FV_PREM_PUT</f>
         <v>221118.055555556</v>
       </c>
-      <c r="D16" s="40" t="n">
+      <c r="D16" s="47" t="n">
         <v>221118.06</v>
       </c>
       <c r="E16" s="15" t="str">
@@ -3625,13 +3818,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C17" s="39" t="n">
+        <v>133</v>
+      </c>
+      <c r="C17" s="46" t="n">
         <f aca="false">MAX(K_PUT,K_PUT)*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
-      <c r="D17" s="39" t="n">
+      <c r="D17" s="46" t="n">
         <f aca="false">K_PUT*FC_AMT-FV_PREM_PUT</f>
         <v>13153881.9444444</v>
       </c>
@@ -3642,13 +3835,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C18" s="39" t="n">
+        <v>134</v>
+      </c>
+      <c r="C18" s="46" t="n">
         <f aca="false">S0_in*FC_AMT</f>
         <v>13375000</v>
       </c>
-      <c r="D18" s="40" t="n">
+      <c r="D18" s="47" t="n">
         <v>13375000</v>
       </c>
       <c r="E18" s="15" t="str">
@@ -3658,13 +3851,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="34" t="n">
+        <v>135</v>
+      </c>
+      <c r="C19" s="41" t="n">
         <f aca="false">Sensitivity!$C$12+Sensitivity!$C$22</f>
         <v>2.14</v>
       </c>
-      <c r="D19" s="34" t="n">
+      <c r="D19" s="41" t="n">
         <f aca="false">2*S0_in</f>
         <v>2.14</v>
       </c>

--- a/models/builds/2026-08-07-Patague-tech-services-model.xlsx
+++ b/models/builds/2026-08-07-Patague-tech-services-model.xlsx
@@ -233,7 +233,7 @@
     <t xml:space="preserve">Inputs — named-range contract</t>
   </si>
   <si>
-    <t xml:space="preserve">All values indicative — replaced with live market data at Stage 4.</t>
+    <t xml:space="preserve">Live market data as of 2026-08-07 (HST); provenance: data/2026-08-07-Patague-market-data.md</t>
   </si>
   <si>
     <t xml:space="preserve">Named range</t>
@@ -257,28 +257,28 @@
     <t xml:space="preserve">USD per EUR</t>
   </si>
   <si>
-    <t xml:space="preserve">ECB reference rate / Yahoo Finance EURUSD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spot + CME/Bloomberg 12-mo forward points</t>
+    <t xml:space="preserve">ECB euro reference rate, 2026-08-07 (~16:00 CET fix)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIP-implied from S0_in, R_USD, R_FC (see data memo)</t>
   </si>
   <si>
     <t xml:space="preserve">Annual %, ACT/360</t>
   </si>
   <si>
-    <t xml:space="preserve">Fed H.15, 1-yr Treasury constant maturity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-mo Euribor (EMMI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set to Stage-4 S0_in; nearest listed CME strike</t>
+    <t xml:space="preserve">FRED DGS1 (1-yr Treasury CMT), obs 2026-08-05, retr. 2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-mo Euribor (EMMI), fixing 2026-08-06, retr. 2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set at live spot per scenario convention</t>
   </si>
   <si>
     <t xml:space="preserve">USD per 1 EUR</t>
   </si>
   <si>
-    <t xml:space="preserve">CME EUR/USD option quotes</t>
+    <t xml:space="preserve">Scenario premium kept — assumption (see data memo)</t>
   </si>
   <si>
     <t xml:space="preserve">Days</t>
@@ -468,7 +468,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="15">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
@@ -480,10 +480,8 @@
     <numFmt numFmtId="172" formatCode="0.000000"/>
     <numFmt numFmtId="173" formatCode="0.00000"/>
     <numFmt numFmtId="174" formatCode="0.0000%"/>
-    <numFmt numFmtId="175" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="176" formatCode="\$#,##0"/>
-    <numFmt numFmtId="177" formatCode="0.0%"/>
-    <numFmt numFmtId="178" formatCode="\$#,##0;&quot;($&quot;#,##0\)"/>
+    <numFmt numFmtId="175" formatCode="0.0%"/>
+    <numFmt numFmtId="176" formatCode="\$#,##0;&quot;($&quot;#,##0\)"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -691,7 +689,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -820,35 +818,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -856,15 +834,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -877,10 +847,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="171" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1072,37 +1038,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1.0165</c:v>
+                  <c:v>1.0958</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0272</c:v>
+                  <c:v>1.1074</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0379</c:v>
+                  <c:v>1.1189</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0486</c:v>
+                  <c:v>1.1304</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0593</c:v>
+                  <c:v>1.1420</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0700</c:v>
+                  <c:v>1.1535</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0807</c:v>
+                  <c:v>1.1650</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0914</c:v>
+                  <c:v>1.1766</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.1021</c:v>
+                  <c:v>1.1881</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.1128</c:v>
+                  <c:v>1.1996</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.1235</c:v>
+                  <c:v>1.2112</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1114,37 +1080,37 @@
                 <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>12706250</c:v>
+                  <c:v>13697812.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12840000</c:v>
+                  <c:v>13842000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12973750</c:v>
+                  <c:v>13986187.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13107500</c:v>
+                  <c:v>14130375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13241250</c:v>
+                  <c:v>14274562.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13375000</c:v>
+                  <c:v>14418750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>13508750</c:v>
+                  <c:v>14562937.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>13642500</c:v>
+                  <c:v>14707125</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>13776250</c:v>
+                  <c:v>14851312.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13910000</c:v>
+                  <c:v>14995500</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14043750</c:v>
+                  <c:v>15139687.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1224,37 +1190,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1.0165</c:v>
+                  <c:v>1.0958</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0272</c:v>
+                  <c:v>1.1074</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0379</c:v>
+                  <c:v>1.1189</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0486</c:v>
+                  <c:v>1.1304</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0593</c:v>
+                  <c:v>1.1420</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0700</c:v>
+                  <c:v>1.1535</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0807</c:v>
+                  <c:v>1.1650</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0914</c:v>
+                  <c:v>1.1766</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.1021</c:v>
+                  <c:v>1.1881</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.1128</c:v>
+                  <c:v>1.1996</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.1235</c:v>
+                  <c:v>1.2112</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1266,37 +1232,37 @@
                 <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>13637500</c:v>
+                  <c:v>14581250</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13637500</c:v>
+                  <c:v>14581250</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13637500</c:v>
+                  <c:v>14581250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13637500</c:v>
+                  <c:v>14581250</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13637500</c:v>
+                  <c:v>14581250</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13637500</c:v>
+                  <c:v>14581250</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>13637500</c:v>
+                  <c:v>14581250</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>13637500</c:v>
+                  <c:v>14581250</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>13637500</c:v>
+                  <c:v>14581250</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13637500</c:v>
+                  <c:v>14581250</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13637500</c:v>
+                  <c:v>14581250</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1376,37 +1342,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1.0165</c:v>
+                  <c:v>1.0958</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0272</c:v>
+                  <c:v>1.1074</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0379</c:v>
+                  <c:v>1.1189</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0486</c:v>
+                  <c:v>1.1304</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0593</c:v>
+                  <c:v>1.1420</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0700</c:v>
+                  <c:v>1.1535</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0807</c:v>
+                  <c:v>1.1650</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0914</c:v>
+                  <c:v>1.1766</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.1021</c:v>
+                  <c:v>1.1881</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.1128</c:v>
+                  <c:v>1.1996</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.1235</c:v>
+                  <c:v>1.2112</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1418,37 +1384,37 @@
                 <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>13640824.9387422</c:v>
+                  <c:v>14581524.2498784</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13640824.9387422</c:v>
+                  <c:v>14581524.2498784</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13640824.9387422</c:v>
+                  <c:v>14581524.2498784</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13640824.9387422</c:v>
+                  <c:v>14581524.2498784</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13640824.9387422</c:v>
+                  <c:v>14581524.2498784</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13640824.9387422</c:v>
+                  <c:v>14581524.2498784</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>13640824.9387422</c:v>
+                  <c:v>14581524.2498784</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>13640824.9387422</c:v>
+                  <c:v>14581524.2498784</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>13640824.9387422</c:v>
+                  <c:v>14581524.2498784</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13640824.9387422</c:v>
+                  <c:v>14581524.2498784</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13640824.9387422</c:v>
+                  <c:v>14581524.2498784</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1528,37 +1494,37 @@
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1.0165</c:v>
+                  <c:v>1.0958</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0272</c:v>
+                  <c:v>1.1074</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0379</c:v>
+                  <c:v>1.1189</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0486</c:v>
+                  <c:v>1.1304</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0593</c:v>
+                  <c:v>1.1420</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0700</c:v>
+                  <c:v>1.1535</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0807</c:v>
+                  <c:v>1.1650</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0914</c:v>
+                  <c:v>1.1766</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.1021</c:v>
+                  <c:v>1.1881</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.1128</c:v>
+                  <c:v>1.1996</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.1235</c:v>
+                  <c:v>1.2112</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1570,37 +1536,37 @@
                 <c:formatCode>\$#,##0</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>13153881.9444444</c:v>
+                  <c:v>14197567.3090278</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13153881.9444444</c:v>
+                  <c:v>14197567.3090278</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13153881.9444444</c:v>
+                  <c:v>14197567.3090278</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13153881.9444444</c:v>
+                  <c:v>14197567.3090278</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13153881.9444444</c:v>
+                  <c:v>14197567.3090278</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13153881.9444444</c:v>
+                  <c:v>14197567.3090278</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>13287631.9444444</c:v>
+                  <c:v>14341754.8090278</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>13421381.9444444</c:v>
+                  <c:v>14485942.3090278</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>13555131.9444444</c:v>
+                  <c:v>14630129.8090278</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13688881.9444444</c:v>
+                  <c:v>14774317.3090278</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13822631.9444444</c:v>
+                  <c:v>14918504.8090278</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1615,11 +1581,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="47287402"/>
-        <c:axId val="63147692"/>
+        <c:axId val="50206171"/>
+        <c:axId val="40969027"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="47287402"/>
+        <c:axId val="50206171"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1685,7 +1651,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63147692"/>
+        <c:crossAx val="40969027"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1693,7 +1659,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="63147692"/>
+        <c:axId val="40969027"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1769,7 +1735,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47287402"/>
+        <c:crossAx val="50206171"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2051,9 +2017,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>447480</xdr:colOff>
+      <xdr:colOff>447120</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>169920</xdr:rowOff>
+      <xdr:rowOff>169560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2062,7 +2028,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="211320" y="4600440"/>
-        <a:ext cx="7918920" cy="3598920"/>
+        <a:ext cx="7918560" cy="3598560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2352,7 +2318,7 @@
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">S0_in*FC_AMT</f>
-        <v>13375000</v>
+        <v>14418750</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>19</v>
@@ -2364,7 +2330,7 @@
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">USD_FWD</f>
-        <v>13637500</v>
+        <v>14581250</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>21</v>
@@ -2376,7 +2342,7 @@
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">USD_MM</f>
-        <v>13640824.9387422</v>
+        <v>14581524.2498784</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>23</v>
@@ -2388,7 +2354,7 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">USD_BASE_PUT</f>
-        <v>13153881.9444444</v>
+        <v>14197567.3090278</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>25</v>
@@ -2400,7 +2366,7 @@
       </c>
       <c r="C22" s="12" t="n">
         <f aca="false">USD_FLOOR_PUT</f>
-        <v>13153881.9444444</v>
+        <v>14197567.3090278</v>
       </c>
     </row>
   </sheetData>
@@ -2625,7 +2591,7 @@
         <v>40</v>
       </c>
       <c r="C7" s="21" t="n">
-        <v>1.07</v>
+        <v>1.1535</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>66</v>
@@ -2639,7 +2605,7 @@
         <v>42</v>
       </c>
       <c r="C8" s="21" t="n">
-        <v>1.091</v>
+        <v>1.1665</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>66</v>
@@ -2653,7 +2619,7 @@
         <v>44</v>
       </c>
       <c r="C9" s="22" t="n">
-        <v>0.04</v>
+        <v>0.0403</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>69</v>
@@ -2667,7 +2633,7 @@
         <v>46</v>
       </c>
       <c r="C10" s="22" t="n">
-        <v>0.02</v>
+        <v>0.02884</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>69</v>
@@ -2681,7 +2647,7 @@
         <v>48</v>
       </c>
       <c r="C11" s="21" t="n">
-        <v>1.07</v>
+        <v>1.1535</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>66</v>
@@ -2695,7 +2661,7 @@
         <v>50</v>
       </c>
       <c r="C12" s="21" t="n">
-        <v>1.07</v>
+        <v>1.1535</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>66</v>
@@ -2786,7 +2752,7 @@
       </c>
       <c r="C5" s="25" t="n">
         <f aca="false">FC_AMT*F0_in</f>
-        <v>13637500</v>
+        <v>14581250</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2834,7 +2800,7 @@
       </c>
       <c r="C5" s="26" t="n">
         <f aca="false">1+R_USD*T_DAYS/360</f>
-        <v>1.04055555555556</v>
+        <v>1.04085972222222</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2843,7 +2809,7 @@
       </c>
       <c r="C6" s="26" t="n">
         <f aca="false">1+R_FC*T_DAYS/360</f>
-        <v>1.02027777777778</v>
+        <v>1.02924055555556</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2852,7 +2818,7 @@
       </c>
       <c r="C8" s="27" t="n">
         <f aca="false">FC_AMT/DF_FC</f>
-        <v>12251565.4778111</v>
+        <v>12144877.0479636</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2861,7 +2827,7 @@
       </c>
       <c r="C9" s="28" t="n">
         <f aca="false">MM_BORROW*S0_in</f>
-        <v>13109175.0612578</v>
+        <v>14009115.674826</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2870,7 +2836,7 @@
       </c>
       <c r="C10" s="25" t="n">
         <f aca="false">MM_USD_NOW*DF_USD</f>
-        <v>13640824.9387422</v>
+        <v>14581524.2498784</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2884,7 +2850,7 @@
       </c>
       <c r="C13" s="29" t="n">
         <f aca="false">S0_in*DF_USD/DF_FC</f>
-        <v>1.09126599509937</v>
+        <v>1.16652193999027</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2893,7 +2859,7 @@
       </c>
       <c r="C14" s="29" t="n">
         <f aca="false">ABS(C13-F0_in)</f>
-        <v>0.00026599509937375</v>
+        <v>2.19399902732231E-005</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2902,11 +2868,11 @@
       </c>
       <c r="C15" s="25" t="n">
         <f aca="false">USD_MM-USD_FWD</f>
-        <v>3324.93874217197</v>
+        <v>274.249878413975</v>
       </c>
       <c r="D15" s="30" t="n">
         <f aca="false">(USD_MM-USD_FWD)/USD_FWD</f>
-        <v>0.000243808523715635</v>
+        <v>1.88083928616528E-005</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2958,7 +2924,7 @@
       </c>
       <c r="C5" s="28" t="n">
         <f aca="false">PREM_PUT*FC_AMT*DF_USD</f>
-        <v>221118.055555556</v>
+        <v>221182.690972222</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2972,7 +2938,7 @@
       </c>
       <c r="C9" s="25" t="n">
         <f aca="false">MAX(S0_in,K_PUT)*FC_AMT-FV_PREM_PUT</f>
-        <v>13153881.9444444</v>
+        <v>14197567.3090278</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2981,7 +2947,7 @@
       </c>
       <c r="C10" s="25" t="n">
         <f aca="false">MIN(Sensitivity!$G$12:$G$22)</f>
-        <v>13153881.9444444</v>
+        <v>14197567.3090278</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2990,7 +2956,7 @@
       </c>
       <c r="C12" s="28" t="n">
         <f aca="false">K_PUT*FC_AMT-FV_PREM_PUT</f>
-        <v>13153881.9444444</v>
+        <v>14197567.3090278</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2998,150 +2964,150 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="32" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="33" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="34" t="n">
+      <c r="C16" s="28" t="n">
         <f aca="false">PREM_CALL*FC_AMT*DF_USD</f>
-        <v>286152.777777778</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="33" t="s">
+        <v>286236.423611111</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="25" t="n">
         <f aca="false">MIN(S0_in,K_CALL)*FC_AMT+FV_PREM_CALL</f>
-        <v>13661152.7777778</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="33" t="s">
+        <v>14704986.4236111</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="36" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="8" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="37" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="32" t="n">
         <f aca="false">Sensitivity!$C$12</f>
-        <v>1.0165</v>
-      </c>
-      <c r="C21" s="38" t="n">
+        <v>1.095825</v>
+      </c>
+      <c r="C21" s="33" t="n">
         <f aca="false">MIN($B21,K_CALL)*FC_AMT+FV_PREM_CALL</f>
-        <v>12992402.7777778</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="37" t="n">
+        <v>13984048.9236111</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="32" t="n">
         <f aca="false">Sensitivity!$C$13</f>
-        <v>1.0272</v>
-      </c>
-      <c r="C22" s="38" t="n">
+        <v>1.10736</v>
+      </c>
+      <c r="C22" s="33" t="n">
         <f aca="false">MIN($B22,K_CALL)*FC_AMT+FV_PREM_CALL</f>
-        <v>13126152.7777778</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="37" t="n">
+        <v>14128236.4236111</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="32" t="n">
         <f aca="false">Sensitivity!$C$14</f>
-        <v>1.0379</v>
-      </c>
-      <c r="C23" s="38" t="n">
+        <v>1.118895</v>
+      </c>
+      <c r="C23" s="33" t="n">
         <f aca="false">MIN($B23,K_CALL)*FC_AMT+FV_PREM_CALL</f>
-        <v>13259902.7777778</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="37" t="n">
+        <v>14272423.9236111</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="32" t="n">
         <f aca="false">Sensitivity!$C$15</f>
-        <v>1.0486</v>
-      </c>
-      <c r="C24" s="38" t="n">
+        <v>1.13043</v>
+      </c>
+      <c r="C24" s="33" t="n">
         <f aca="false">MIN($B24,K_CALL)*FC_AMT+FV_PREM_CALL</f>
-        <v>13393652.7777778</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="37" t="n">
+        <v>14416611.4236111</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="32" t="n">
         <f aca="false">Sensitivity!$C$16</f>
-        <v>1.0593</v>
-      </c>
-      <c r="C25" s="38" t="n">
+        <v>1.141965</v>
+      </c>
+      <c r="C25" s="33" t="n">
         <f aca="false">MIN($B25,K_CALL)*FC_AMT+FV_PREM_CALL</f>
-        <v>13527402.7777778</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="37" t="n">
+        <v>14560798.9236111</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="32" t="n">
         <f aca="false">Sensitivity!$C$17</f>
-        <v>1.07</v>
-      </c>
-      <c r="C26" s="38" t="n">
+        <v>1.1535</v>
+      </c>
+      <c r="C26" s="33" t="n">
         <f aca="false">MIN($B26,K_CALL)*FC_AMT+FV_PREM_CALL</f>
-        <v>13661152.7777778</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="37" t="n">
+        <v>14704986.4236111</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="32" t="n">
         <f aca="false">Sensitivity!$C$18</f>
-        <v>1.0807</v>
-      </c>
-      <c r="C27" s="38" t="n">
+        <v>1.165035</v>
+      </c>
+      <c r="C27" s="33" t="n">
         <f aca="false">MIN($B27,K_CALL)*FC_AMT+FV_PREM_CALL</f>
-        <v>13661152.7777778</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="37" t="n">
+        <v>14704986.4236111</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="32" t="n">
         <f aca="false">Sensitivity!$C$19</f>
-        <v>1.0914</v>
-      </c>
-      <c r="C28" s="38" t="n">
+        <v>1.17657</v>
+      </c>
+      <c r="C28" s="33" t="n">
         <f aca="false">MIN($B28,K_CALL)*FC_AMT+FV_PREM_CALL</f>
-        <v>13661152.7777778</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="37" t="n">
+        <v>14704986.4236111</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="32" t="n">
         <f aca="false">Sensitivity!$C$20</f>
-        <v>1.1021</v>
-      </c>
-      <c r="C29" s="38" t="n">
+        <v>1.188105</v>
+      </c>
+      <c r="C29" s="33" t="n">
         <f aca="false">MIN($B29,K_CALL)*FC_AMT+FV_PREM_CALL</f>
-        <v>13661152.7777778</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="37" t="n">
+        <v>14704986.4236111</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="32" t="n">
         <f aca="false">Sensitivity!$C$21</f>
-        <v>1.1128</v>
-      </c>
-      <c r="C30" s="38" t="n">
+        <v>1.19964</v>
+      </c>
+      <c r="C30" s="33" t="n">
         <f aca="false">MIN($B30,K_CALL)*FC_AMT+FV_PREM_CALL</f>
-        <v>13661152.7777778</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="37" t="n">
+        <v>14704986.4236111</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="32" t="n">
         <f aca="false">Sensitivity!$C$22</f>
-        <v>1.1235</v>
-      </c>
-      <c r="C31" s="38" t="n">
+        <v>1.211175</v>
+      </c>
+      <c r="C31" s="33" t="n">
         <f aca="false">MIN($B31,K_CALL)*FC_AMT+FV_PREM_CALL</f>
-        <v>13661152.7777778</v>
+        <v>14704986.4236111</v>
       </c>
     </row>
   </sheetData>
@@ -3180,7 +3146,7 @@
       <c r="B4" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="39" t="n">
+      <c r="C4" s="34" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3217,40 +3183,40 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="40" t="n">
+      <c r="B12" s="35" t="n">
         <v>-5</v>
       </c>
-      <c r="C12" s="41" t="n">
+      <c r="C12" s="32" t="n">
         <f aca="false">S0_in*(1+$B12*STEP_FRAC)</f>
-        <v>1.0165</v>
-      </c>
-      <c r="D12" s="42" t="n">
+        <v>1.095825</v>
+      </c>
+      <c r="D12" s="33" t="n">
         <f aca="false">$C12*FC_AMT</f>
-        <v>12706250</v>
-      </c>
-      <c r="E12" s="42" t="n">
+        <v>13697812.5</v>
+      </c>
+      <c r="E12" s="33" t="n">
         <f aca="false">USD_FWD</f>
-        <v>13637500</v>
-      </c>
-      <c r="F12" s="42" t="n">
+        <v>14581250</v>
+      </c>
+      <c r="F12" s="33" t="n">
         <f aca="false">USD_MM</f>
-        <v>13640824.9387422</v>
-      </c>
-      <c r="G12" s="42" t="n">
+        <v>14581524.2498784</v>
+      </c>
+      <c r="G12" s="33" t="n">
         <f aca="false">MAX($C12,K_PUT)*FC_AMT-FV_PREM_PUT</f>
-        <v>13153881.9444444</v>
-      </c>
-      <c r="H12" s="43" t="n">
+        <v>14197567.3090278</v>
+      </c>
+      <c r="H12" s="36" t="n">
         <f aca="false">$E12-$D12</f>
-        <v>931250</v>
-      </c>
-      <c r="I12" s="43" t="n">
+        <v>883437.500000004</v>
+      </c>
+      <c r="I12" s="36" t="n">
         <f aca="false">$F12-$D12</f>
-        <v>934574.938742172</v>
-      </c>
-      <c r="J12" s="43" t="n">
+        <v>883711.749878418</v>
+      </c>
+      <c r="J12" s="36" t="n">
         <f aca="false">$G12-$D12</f>
-        <v>447631.944444444</v>
+        <v>499754.80902778</v>
       </c>
       <c r="K12" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D12:$G12),$D12:$G12,0))</f>
@@ -3258,40 +3224,40 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="40" t="n">
+      <c r="B13" s="35" t="n">
         <v>-4</v>
       </c>
-      <c r="C13" s="41" t="n">
+      <c r="C13" s="32" t="n">
         <f aca="false">S0_in*(1+$B13*STEP_FRAC)</f>
-        <v>1.0272</v>
-      </c>
-      <c r="D13" s="42" t="n">
+        <v>1.10736</v>
+      </c>
+      <c r="D13" s="33" t="n">
         <f aca="false">$C13*FC_AMT</f>
-        <v>12840000</v>
-      </c>
-      <c r="E13" s="42" t="n">
+        <v>13842000</v>
+      </c>
+      <c r="E13" s="33" t="n">
         <f aca="false">USD_FWD</f>
-        <v>13637500</v>
-      </c>
-      <c r="F13" s="42" t="n">
+        <v>14581250</v>
+      </c>
+      <c r="F13" s="33" t="n">
         <f aca="false">USD_MM</f>
-        <v>13640824.9387422</v>
-      </c>
-      <c r="G13" s="42" t="n">
+        <v>14581524.2498784</v>
+      </c>
+      <c r="G13" s="33" t="n">
         <f aca="false">MAX($C13,K_PUT)*FC_AMT-FV_PREM_PUT</f>
-        <v>13153881.9444444</v>
-      </c>
-      <c r="H13" s="43" t="n">
+        <v>14197567.3090278</v>
+      </c>
+      <c r="H13" s="36" t="n">
         <f aca="false">$E13-$D13</f>
-        <v>797499.999999998</v>
-      </c>
-      <c r="I13" s="43" t="n">
+        <v>739250.000000004</v>
+      </c>
+      <c r="I13" s="36" t="n">
         <f aca="false">$F13-$D13</f>
-        <v>800824.93874217</v>
-      </c>
-      <c r="J13" s="43" t="n">
+        <v>739524.249878418</v>
+      </c>
+      <c r="J13" s="36" t="n">
         <f aca="false">$G13-$D13</f>
-        <v>313881.944444442</v>
+        <v>355567.30902778</v>
       </c>
       <c r="K13" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D13:$G13),$D13:$G13,0))</f>
@@ -3299,40 +3265,40 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="40" t="n">
+      <c r="B14" s="35" t="n">
         <v>-3</v>
       </c>
-      <c r="C14" s="41" t="n">
+      <c r="C14" s="32" t="n">
         <f aca="false">S0_in*(1+$B14*STEP_FRAC)</f>
-        <v>1.0379</v>
-      </c>
-      <c r="D14" s="42" t="n">
+        <v>1.118895</v>
+      </c>
+      <c r="D14" s="33" t="n">
         <f aca="false">$C14*FC_AMT</f>
-        <v>12973750</v>
-      </c>
-      <c r="E14" s="42" t="n">
+        <v>13986187.5</v>
+      </c>
+      <c r="E14" s="33" t="n">
         <f aca="false">USD_FWD</f>
-        <v>13637500</v>
-      </c>
-      <c r="F14" s="42" t="n">
+        <v>14581250</v>
+      </c>
+      <c r="F14" s="33" t="n">
         <f aca="false">USD_MM</f>
-        <v>13640824.9387422</v>
-      </c>
-      <c r="G14" s="42" t="n">
+        <v>14581524.2498784</v>
+      </c>
+      <c r="G14" s="33" t="n">
         <f aca="false">MAX($C14,K_PUT)*FC_AMT-FV_PREM_PUT</f>
-        <v>13153881.9444444</v>
-      </c>
-      <c r="H14" s="43" t="n">
+        <v>14197567.3090278</v>
+      </c>
+      <c r="H14" s="36" t="n">
         <f aca="false">$E14-$D14</f>
-        <v>663750</v>
-      </c>
-      <c r="I14" s="43" t="n">
+        <v>595062.500000002</v>
+      </c>
+      <c r="I14" s="36" t="n">
         <f aca="false">$F14-$D14</f>
-        <v>667074.938742172</v>
-      </c>
-      <c r="J14" s="43" t="n">
+        <v>595336.749878416</v>
+      </c>
+      <c r="J14" s="36" t="n">
         <f aca="false">$G14-$D14</f>
-        <v>180131.944444444</v>
+        <v>211379.809027778</v>
       </c>
       <c r="K14" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D14:$G14),$D14:$G14,0))</f>
@@ -3340,40 +3306,40 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="40" t="n">
+      <c r="B15" s="35" t="n">
         <v>-2</v>
       </c>
-      <c r="C15" s="41" t="n">
+      <c r="C15" s="32" t="n">
         <f aca="false">S0_in*(1+$B15*STEP_FRAC)</f>
-        <v>1.0486</v>
-      </c>
-      <c r="D15" s="42" t="n">
+        <v>1.13043</v>
+      </c>
+      <c r="D15" s="33" t="n">
         <f aca="false">$C15*FC_AMT</f>
-        <v>13107500</v>
-      </c>
-      <c r="E15" s="42" t="n">
+        <v>14130375</v>
+      </c>
+      <c r="E15" s="33" t="n">
         <f aca="false">USD_FWD</f>
-        <v>13637500</v>
-      </c>
-      <c r="F15" s="42" t="n">
+        <v>14581250</v>
+      </c>
+      <c r="F15" s="33" t="n">
         <f aca="false">USD_MM</f>
-        <v>13640824.9387422</v>
-      </c>
-      <c r="G15" s="42" t="n">
+        <v>14581524.2498784</v>
+      </c>
+      <c r="G15" s="33" t="n">
         <f aca="false">MAX($C15,K_PUT)*FC_AMT-FV_PREM_PUT</f>
-        <v>13153881.9444444</v>
-      </c>
-      <c r="H15" s="43" t="n">
+        <v>14197567.3090278</v>
+      </c>
+      <c r="H15" s="36" t="n">
         <f aca="false">$E15-$D15</f>
-        <v>530000</v>
-      </c>
-      <c r="I15" s="43" t="n">
+        <v>450875.000000002</v>
+      </c>
+      <c r="I15" s="36" t="n">
         <f aca="false">$F15-$D15</f>
-        <v>533324.938742172</v>
-      </c>
-      <c r="J15" s="43" t="n">
+        <v>451149.249878416</v>
+      </c>
+      <c r="J15" s="36" t="n">
         <f aca="false">$G15-$D15</f>
-        <v>46381.944444444</v>
+        <v>67192.309027778</v>
       </c>
       <c r="K15" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D15:$G15),$D15:$G15,0))</f>
@@ -3381,40 +3347,40 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="40" t="n">
+      <c r="B16" s="35" t="n">
         <v>-1</v>
       </c>
-      <c r="C16" s="41" t="n">
+      <c r="C16" s="32" t="n">
         <f aca="false">S0_in*(1+$B16*STEP_FRAC)</f>
-        <v>1.0593</v>
-      </c>
-      <c r="D16" s="42" t="n">
+        <v>1.141965</v>
+      </c>
+      <c r="D16" s="33" t="n">
         <f aca="false">$C16*FC_AMT</f>
-        <v>13241250</v>
-      </c>
-      <c r="E16" s="42" t="n">
+        <v>14274562.5</v>
+      </c>
+      <c r="E16" s="33" t="n">
         <f aca="false">USD_FWD</f>
-        <v>13637500</v>
-      </c>
-      <c r="F16" s="42" t="n">
+        <v>14581250</v>
+      </c>
+      <c r="F16" s="33" t="n">
         <f aca="false">USD_MM</f>
-        <v>13640824.9387422</v>
-      </c>
-      <c r="G16" s="42" t="n">
+        <v>14581524.2498784</v>
+      </c>
+      <c r="G16" s="33" t="n">
         <f aca="false">MAX($C16,K_PUT)*FC_AMT-FV_PREM_PUT</f>
-        <v>13153881.9444444</v>
-      </c>
-      <c r="H16" s="43" t="n">
+        <v>14197567.3090278</v>
+      </c>
+      <c r="H16" s="36" t="n">
         <f aca="false">$E16-$D16</f>
-        <v>396249.999999998</v>
-      </c>
-      <c r="I16" s="43" t="n">
+        <v>306687.500000004</v>
+      </c>
+      <c r="I16" s="36" t="n">
         <f aca="false">$F16-$D16</f>
-        <v>399574.93874217</v>
-      </c>
-      <c r="J16" s="43" t="n">
+        <v>306961.749878418</v>
+      </c>
+      <c r="J16" s="36" t="n">
         <f aca="false">$G16-$D16</f>
-        <v>-87368.0555555578</v>
+        <v>-76995.1909722202</v>
       </c>
       <c r="K16" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D16:$G16),$D16:$G16,0))</f>
@@ -3422,84 +3388,84 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="40" t="n">
+      <c r="B17" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="41" t="n">
+      <c r="C17" s="32" t="n">
         <f aca="false">S0_in*(1+$B17*STEP_FRAC)</f>
-        <v>1.07</v>
-      </c>
-      <c r="D17" s="42" t="n">
+        <v>1.1535</v>
+      </c>
+      <c r="D17" s="33" t="n">
         <f aca="false">$C17*FC_AMT</f>
-        <v>13375000</v>
-      </c>
-      <c r="E17" s="42" t="n">
+        <v>14418750</v>
+      </c>
+      <c r="E17" s="33" t="n">
         <f aca="false">USD_FWD</f>
-        <v>13637500</v>
-      </c>
-      <c r="F17" s="42" t="n">
+        <v>14581250</v>
+      </c>
+      <c r="F17" s="33" t="n">
         <f aca="false">USD_MM</f>
-        <v>13640824.9387422</v>
-      </c>
-      <c r="G17" s="42" t="n">
+        <v>14581524.2498784</v>
+      </c>
+      <c r="G17" s="33" t="n">
         <f aca="false">MAX($C17,K_PUT)*FC_AMT-FV_PREM_PUT</f>
-        <v>13153881.9444444</v>
-      </c>
-      <c r="H17" s="43" t="n">
+        <v>14197567.3090278</v>
+      </c>
+      <c r="H17" s="36" t="n">
         <f aca="false">$E17-$D17</f>
-        <v>262500</v>
-      </c>
-      <c r="I17" s="43" t="n">
+        <v>162500.000000002</v>
+      </c>
+      <c r="I17" s="36" t="n">
         <f aca="false">$F17-$D17</f>
-        <v>265824.938742172</v>
-      </c>
-      <c r="J17" s="43" t="n">
+        <v>162774.249878416</v>
+      </c>
+      <c r="J17" s="36" t="n">
         <f aca="false">$G17-$D17</f>
-        <v>-221118.055555556</v>
+        <v>-221182.690972222</v>
       </c>
       <c r="K17" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D17:$G17),$D17:$G17,0))</f>
         <v>Money mkt</v>
       </c>
-      <c r="L17" s="44" t="s">
+      <c r="L17" s="37" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="40" t="n">
+      <c r="B18" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="41" t="n">
+      <c r="C18" s="32" t="n">
         <f aca="false">S0_in*(1+$B18*STEP_FRAC)</f>
-        <v>1.0807</v>
-      </c>
-      <c r="D18" s="42" t="n">
+        <v>1.165035</v>
+      </c>
+      <c r="D18" s="33" t="n">
         <f aca="false">$C18*FC_AMT</f>
-        <v>13508750</v>
-      </c>
-      <c r="E18" s="42" t="n">
+        <v>14562937.5</v>
+      </c>
+      <c r="E18" s="33" t="n">
         <f aca="false">USD_FWD</f>
-        <v>13637500</v>
-      </c>
-      <c r="F18" s="42" t="n">
+        <v>14581250</v>
+      </c>
+      <c r="F18" s="33" t="n">
         <f aca="false">USD_MM</f>
-        <v>13640824.9387422</v>
-      </c>
-      <c r="G18" s="42" t="n">
+        <v>14581524.2498784</v>
+      </c>
+      <c r="G18" s="33" t="n">
         <f aca="false">MAX($C18,K_PUT)*FC_AMT-FV_PREM_PUT</f>
-        <v>13287631.9444444</v>
-      </c>
-      <c r="H18" s="43" t="n">
+        <v>14341754.8090278</v>
+      </c>
+      <c r="H18" s="36" t="n">
         <f aca="false">$E18-$D18</f>
-        <v>128750</v>
-      </c>
-      <c r="I18" s="43" t="n">
+        <v>18312.5000000019</v>
+      </c>
+      <c r="I18" s="36" t="n">
         <f aca="false">$F18-$D18</f>
-        <v>132074.938742172</v>
-      </c>
-      <c r="J18" s="43" t="n">
+        <v>18586.7498784158</v>
+      </c>
+      <c r="J18" s="36" t="n">
         <f aca="false">$G18-$D18</f>
-        <v>-221118.055555556</v>
+        <v>-221182.690972222</v>
       </c>
       <c r="K18" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D18:$G18),$D18:$G18,0))</f>
@@ -3507,40 +3473,40 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="40" t="n">
+      <c r="B19" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="41" t="n">
+      <c r="C19" s="32" t="n">
         <f aca="false">S0_in*(1+$B19*STEP_FRAC)</f>
-        <v>1.0914</v>
-      </c>
-      <c r="D19" s="42" t="n">
+        <v>1.17657</v>
+      </c>
+      <c r="D19" s="33" t="n">
         <f aca="false">$C19*FC_AMT</f>
-        <v>13642500</v>
-      </c>
-      <c r="E19" s="42" t="n">
+        <v>14707125</v>
+      </c>
+      <c r="E19" s="33" t="n">
         <f aca="false">USD_FWD</f>
-        <v>13637500</v>
-      </c>
-      <c r="F19" s="42" t="n">
+        <v>14581250</v>
+      </c>
+      <c r="F19" s="33" t="n">
         <f aca="false">USD_MM</f>
-        <v>13640824.9387422</v>
-      </c>
-      <c r="G19" s="42" t="n">
+        <v>14581524.2498784</v>
+      </c>
+      <c r="G19" s="33" t="n">
         <f aca="false">MAX($C19,K_PUT)*FC_AMT-FV_PREM_PUT</f>
-        <v>13421381.9444444</v>
-      </c>
-      <c r="H19" s="43" t="n">
+        <v>14485942.3090278</v>
+      </c>
+      <c r="H19" s="36" t="n">
         <f aca="false">$E19-$D19</f>
-        <v>-5000.00000000186</v>
-      </c>
-      <c r="I19" s="43" t="n">
+        <v>-125874.999999996</v>
+      </c>
+      <c r="I19" s="36" t="n">
         <f aca="false">$F19-$D19</f>
-        <v>-1675.06125782989</v>
-      </c>
-      <c r="J19" s="43" t="n">
+        <v>-125600.750121582</v>
+      </c>
+      <c r="J19" s="36" t="n">
         <f aca="false">$G19-$D19</f>
-        <v>-221118.055555556</v>
+        <v>-221182.690972222</v>
       </c>
       <c r="K19" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D19:$G19),$D19:$G19,0))</f>
@@ -3548,40 +3514,40 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="40" t="n">
+      <c r="B20" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="41" t="n">
+      <c r="C20" s="32" t="n">
         <f aca="false">S0_in*(1+$B20*STEP_FRAC)</f>
-        <v>1.1021</v>
-      </c>
-      <c r="D20" s="42" t="n">
+        <v>1.188105</v>
+      </c>
+      <c r="D20" s="33" t="n">
         <f aca="false">$C20*FC_AMT</f>
-        <v>13776250</v>
-      </c>
-      <c r="E20" s="42" t="n">
+        <v>14851312.5</v>
+      </c>
+      <c r="E20" s="33" t="n">
         <f aca="false">USD_FWD</f>
-        <v>13637500</v>
-      </c>
-      <c r="F20" s="42" t="n">
+        <v>14581250</v>
+      </c>
+      <c r="F20" s="33" t="n">
         <f aca="false">USD_MM</f>
-        <v>13640824.9387422</v>
-      </c>
-      <c r="G20" s="42" t="n">
+        <v>14581524.2498784</v>
+      </c>
+      <c r="G20" s="33" t="n">
         <f aca="false">MAX($C20,K_PUT)*FC_AMT-FV_PREM_PUT</f>
-        <v>13555131.9444444</v>
-      </c>
-      <c r="H20" s="43" t="n">
+        <v>14630129.8090278</v>
+      </c>
+      <c r="H20" s="36" t="n">
         <f aca="false">$E20-$D20</f>
-        <v>-138750.000000002</v>
-      </c>
-      <c r="I20" s="43" t="n">
+        <v>-270062.499999998</v>
+      </c>
+      <c r="I20" s="36" t="n">
         <f aca="false">$F20-$D20</f>
-        <v>-135425.06125783</v>
-      </c>
-      <c r="J20" s="43" t="n">
+        <v>-269788.250121584</v>
+      </c>
+      <c r="J20" s="36" t="n">
         <f aca="false">$G20-$D20</f>
-        <v>-221118.055555556</v>
+        <v>-221182.690972222</v>
       </c>
       <c r="K20" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D20:$G20),$D20:$G20,0))</f>
@@ -3589,40 +3555,40 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="40" t="n">
+      <c r="B21" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="41" t="n">
+      <c r="C21" s="32" t="n">
         <f aca="false">S0_in*(1+$B21*STEP_FRAC)</f>
-        <v>1.1128</v>
-      </c>
-      <c r="D21" s="42" t="n">
+        <v>1.19964</v>
+      </c>
+      <c r="D21" s="33" t="n">
         <f aca="false">$C21*FC_AMT</f>
-        <v>13910000</v>
-      </c>
-      <c r="E21" s="42" t="n">
+        <v>14995500</v>
+      </c>
+      <c r="E21" s="33" t="n">
         <f aca="false">USD_FWD</f>
-        <v>13637500</v>
-      </c>
-      <c r="F21" s="42" t="n">
+        <v>14581250</v>
+      </c>
+      <c r="F21" s="33" t="n">
         <f aca="false">USD_MM</f>
-        <v>13640824.9387422</v>
-      </c>
-      <c r="G21" s="42" t="n">
+        <v>14581524.2498784</v>
+      </c>
+      <c r="G21" s="33" t="n">
         <f aca="false">MAX($C21,K_PUT)*FC_AMT-FV_PREM_PUT</f>
-        <v>13688881.9444444</v>
-      </c>
-      <c r="H21" s="43" t="n">
+        <v>14774317.3090278</v>
+      </c>
+      <c r="H21" s="36" t="n">
         <f aca="false">$E21-$D21</f>
-        <v>-272500</v>
-      </c>
-      <c r="I21" s="43" t="n">
+        <v>-414249.999999998</v>
+      </c>
+      <c r="I21" s="36" t="n">
         <f aca="false">$F21-$D21</f>
-        <v>-269175.061257828</v>
-      </c>
-      <c r="J21" s="43" t="n">
+        <v>-413975.750121584</v>
+      </c>
+      <c r="J21" s="36" t="n">
         <f aca="false">$G21-$D21</f>
-        <v>-221118.055555556</v>
+        <v>-221182.690972222</v>
       </c>
       <c r="K21" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D21:$G21),$D21:$G21,0))</f>
@@ -3630,40 +3596,40 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="40" t="n">
+      <c r="B22" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="41" t="n">
+      <c r="C22" s="32" t="n">
         <f aca="false">S0_in*(1+$B22*STEP_FRAC)</f>
-        <v>1.1235</v>
-      </c>
-      <c r="D22" s="42" t="n">
+        <v>1.211175</v>
+      </c>
+      <c r="D22" s="33" t="n">
         <f aca="false">$C22*FC_AMT</f>
-        <v>14043750</v>
-      </c>
-      <c r="E22" s="42" t="n">
+        <v>15139687.5</v>
+      </c>
+      <c r="E22" s="33" t="n">
         <f aca="false">USD_FWD</f>
-        <v>13637500</v>
-      </c>
-      <c r="F22" s="42" t="n">
+        <v>14581250</v>
+      </c>
+      <c r="F22" s="33" t="n">
         <f aca="false">USD_MM</f>
-        <v>13640824.9387422</v>
-      </c>
-      <c r="G22" s="42" t="n">
+        <v>14581524.2498784</v>
+      </c>
+      <c r="G22" s="33" t="n">
         <f aca="false">MAX($C22,K_PUT)*FC_AMT-FV_PREM_PUT</f>
-        <v>13822631.9444444</v>
-      </c>
-      <c r="H22" s="43" t="n">
+        <v>14918504.8090278</v>
+      </c>
+      <c r="H22" s="36" t="n">
         <f aca="false">$E22-$D22</f>
-        <v>-406250.000000002</v>
-      </c>
-      <c r="I22" s="43" t="n">
+        <v>-558437.5</v>
+      </c>
+      <c r="I22" s="36" t="n">
         <f aca="false">$F22-$D22</f>
-        <v>-402925.06125783</v>
-      </c>
-      <c r="J22" s="43" t="n">
+        <v>-558163.250121586</v>
+      </c>
+      <c r="J22" s="36" t="n">
         <f aca="false">$G22-$D22</f>
-        <v>-221118.055555556</v>
+        <v>-221182.690972222</v>
       </c>
       <c r="K22" s="15" t="str">
         <f aca="false">INDEX($D$11:$G$11,MATCH(MAX($D22:$G22),$D22:$G22,0))</f>
@@ -3754,13 +3720,13 @@
       <c r="B13" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="45" t="n">
+      <c r="C13" s="38" t="n">
         <f aca="false">S0_in*DF_USD/DF_FC</f>
-        <v>1.09126599509937</v>
-      </c>
-      <c r="D13" s="45" t="n">
+        <v>1.16652193999027</v>
+      </c>
+      <c r="D13" s="38" t="n">
         <f aca="false">F0_in</f>
-        <v>1.091</v>
+        <v>1.1665</v>
       </c>
       <c r="E13" s="15" t="str">
         <f aca="false">IF(ABS(C13-D13)&lt;=0.0025,"PASS","FAIL")</f>
@@ -3771,13 +3737,13 @@
       <c r="B14" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="46" t="n">
+      <c r="C14" s="39" t="n">
         <f aca="false">USD_MM</f>
-        <v>13640824.9387422</v>
-      </c>
-      <c r="D14" s="46" t="n">
+        <v>14581524.2498784</v>
+      </c>
+      <c r="D14" s="39" t="n">
         <f aca="false">USD_FWD</f>
-        <v>13637500</v>
+        <v>14581250</v>
       </c>
       <c r="E14" s="15" t="str">
         <f aca="false">IF(ABS(C14-D14)/D14&lt;=0.0005,"PASS","FAIL")</f>
@@ -3788,12 +3754,13 @@
       <c r="B15" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="C15" s="46" t="n">
+      <c r="C15" s="39" t="n">
         <f aca="false">USD_FWD</f>
-        <v>13637500</v>
-      </c>
-      <c r="D15" s="47" t="n">
-        <v>13637500</v>
+        <v>14581250</v>
+      </c>
+      <c r="D15" s="39" t="n">
+        <f aca="false">FC_AMT*F0_in</f>
+        <v>14581250</v>
       </c>
       <c r="E15" s="15" t="str">
         <f aca="false">IF(ABS(C15-D15)&lt;=1,"PASS","FAIL")</f>
@@ -3804,12 +3771,13 @@
       <c r="B16" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C16" s="46" t="n">
+      <c r="C16" s="39" t="n">
         <f aca="false">FV_PREM_PUT</f>
-        <v>221118.055555556</v>
-      </c>
-      <c r="D16" s="47" t="n">
-        <v>221118.06</v>
+        <v>221182.690972222</v>
+      </c>
+      <c r="D16" s="39" t="n">
+        <f aca="false">PREM_PUT*FC_AMT*(1+R_USD*T_DAYS/360)</f>
+        <v>221182.690972222</v>
       </c>
       <c r="E16" s="15" t="str">
         <f aca="false">IF(ABS(C16-D16)&lt;=1,"PASS","FAIL")</f>
@@ -3820,13 +3788,13 @@
       <c r="B17" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="C17" s="46" t="n">
+      <c r="C17" s="39" t="n">
         <f aca="false">MAX(K_PUT,K_PUT)*FC_AMT-FV_PREM_PUT</f>
-        <v>13153881.9444444</v>
-      </c>
-      <c r="D17" s="46" t="n">
+        <v>14197567.3090278</v>
+      </c>
+      <c r="D17" s="39" t="n">
         <f aca="false">K_PUT*FC_AMT-FV_PREM_PUT</f>
-        <v>13153881.9444444</v>
+        <v>14197567.3090278</v>
       </c>
       <c r="E17" s="15" t="str">
         <f aca="false">IF(ABS(C17-D17)&lt;=0.01,"PASS","FAIL")</f>
@@ -3837,12 +3805,13 @@
       <c r="B18" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="46" t="n">
+      <c r="C18" s="39" t="n">
         <f aca="false">S0_in*FC_AMT</f>
-        <v>13375000</v>
-      </c>
-      <c r="D18" s="47" t="n">
-        <v>13375000</v>
+        <v>14418750</v>
+      </c>
+      <c r="D18" s="39" t="n">
+        <f aca="false">S0_in*FC_AMT</f>
+        <v>14418750</v>
       </c>
       <c r="E18" s="15" t="str">
         <f aca="false">IF(ABS(C18-D18)&lt;=1,"PASS","FAIL")</f>
@@ -3853,13 +3822,13 @@
       <c r="B19" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="41" t="n">
+      <c r="C19" s="32" t="n">
         <f aca="false">Sensitivity!$C$12+Sensitivity!$C$22</f>
-        <v>2.14</v>
-      </c>
-      <c r="D19" s="41" t="n">
+        <v>2.307</v>
+      </c>
+      <c r="D19" s="32" t="n">
         <f aca="false">2*S0_in</f>
-        <v>2.14</v>
+        <v>2.307</v>
       </c>
       <c r="E19" s="15" t="str">
         <f aca="false">IF(ABS(C19-D19)&lt;=0.000001,"PASS","FAIL")</f>
